--- a/model/Black_Box_Co_Model.xlsx
+++ b/model/Black_Box_Co_Model.xlsx
@@ -662,7 +662,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1317,6 +1317,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1858,7 +1859,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="B12" s="174" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="13">
       <c r="B13" s="182" t="inlineStr">
         <is>
-          <t>DCF (intrinsic; WACC ~15.1%, g 6%)</t>
+          <t>DCF (intrinsic; WACC ~13.9%, g 5%, mid-year)</t>
         </is>
       </c>
       <c r="C13" s="183">
@@ -1919,7 +1919,6 @@
       </c>
       <c r="C17" s="172" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="B19" s="194" t="inlineStr">
         <is>
@@ -1938,7 +1937,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="B22" s="194" t="inlineStr">
         <is>
@@ -1996,7 +1994,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="B30" s="200" t="inlineStr">
         <is>
@@ -2081,7 +2078,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="B38" s="194" t="inlineStr">
         <is>
@@ -2132,7 +2128,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="B45" s="194" t="inlineStr">
         <is>
@@ -2219,7 +2214,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -5574,7 +5568,6 @@
         <v/>
       </c>
     </row>
-    <row r="120"/>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
@@ -5596,7 +5589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="40.6640625" bestFit="1" customWidth="1" style="132" min="1" max="1"/>
@@ -5611,7 +5604,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="A3" s="57" t="inlineStr">
         <is>
@@ -7033,6 +7025,73 @@
       <c r="P36" s="212" t="n"/>
       <c r="Q36" s="212" t="n"/>
       <c r="R36" s="212" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="94" t="inlineStr">
+        <is>
+          <t>SECTION 7 — CONTRACT ACCOUNTING (Ind-AS 115) - INR cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Contract Assets (unbilled revenue)</t>
+        </is>
+      </c>
+      <c r="G39" s="262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="262" t="n">
+        <v>44</v>
+      </c>
+      <c r="I39" s="262" t="n">
+        <v>114</v>
+      </c>
+      <c r="J39" s="262" t="n">
+        <v>246</v>
+      </c>
+      <c r="K39" s="262" t="n">
+        <v>219</v>
+      </c>
+      <c r="L39" s="262" t="n">
+        <v>280</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>scaled w/ revenue in Forecast (other CA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Contract Liabilities (deferred revenue/advances)</t>
+        </is>
+      </c>
+      <c r="G40" s="262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="262" t="n">
+        <v>523</v>
+      </c>
+      <c r="I40" s="262" t="n">
+        <v>560</v>
+      </c>
+      <c r="J40" s="262" t="n">
+        <v>555</v>
+      </c>
+      <c r="K40" s="262" t="n">
+        <v>500</v>
+      </c>
+      <c r="L40" s="262" t="n">
+        <v>576</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>scaled w/ revenue in Forecast (other CL)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7064,7 +7123,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="A3" s="57" t="inlineStr">
         <is>
@@ -7374,28 +7432,28 @@
       </c>
       <c r="C12" s="59" t="n"/>
       <c r="D12" s="213" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="E12" s="213" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="F12" s="213" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="G12" s="213" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="H12" s="213" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="I12" s="213" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Capex % of revenue</t>
+          <t>Capex incl. ROU/lease &amp; intangible additions (pure cash capex ~0.7-1.0%)</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -7408,28 +7466,28 @@
         <v/>
       </c>
       <c r="D13" s="213" t="n">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="E13" s="213" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="F13" s="213" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="G13" s="213" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="H13" s="213" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="I13" s="213" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Effective tax rate (NOL depletion -&gt; normalising)</t>
+          <t>Effective tax rate (NOL depletion -&gt; statutory ~25%)</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -7442,19 +7500,19 @@
         <v>0.12</v>
       </c>
       <c r="E14" s="213" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="F14" s="213" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="G14" s="213" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H14" s="213" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="I14" s="213" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -7839,7 +7897,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="A29" s="57" t="inlineStr">
         <is>
@@ -14798,11 +14855,11 @@
     <row r="6">
       <c r="A6" s="88" t="inlineStr">
         <is>
-          <t>Beta (small-cap digital-infra integrator, incl. size/specific risk)</t>
+          <t>Beta (small-cap integrator; moderated from 1.30 toward sector norms)</t>
         </is>
       </c>
       <c r="B6" s="137" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
@@ -14895,11 +14952,11 @@
     <row r="16">
       <c r="A16" s="86" t="inlineStr">
         <is>
-          <t>Terminal growth rate (g) — long-run INR nominal (mature global integrator)</t>
+          <t>Terminal growth rate (g) - long-run INR nominal (USD-centric, mature)</t>
         </is>
       </c>
       <c r="B16" s="228" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
@@ -14933,7 +14990,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="A21" s="83" t="inlineStr">
         <is>
@@ -15284,31 +15340,31 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Discount factor @ WACC</t>
+          <t>Discount factor @ WACC (mid-year convention)</t>
         </is>
       </c>
       <c r="B32" s="71">
-        <f>1/(1+$B$13)^1</f>
+        <f>1/(1+$B$13)^0.5</f>
         <v/>
       </c>
       <c r="C32" s="71">
-        <f>1/(1+$B$13)^2</f>
+        <f>1/(1+$B$13)^1.5</f>
         <v/>
       </c>
       <c r="D32" s="71">
-        <f>1/(1+$B$13)^3</f>
+        <f>1/(1+$B$13)^2.5</f>
         <v/>
       </c>
       <c r="E32" s="71">
-        <f>1/(1+$B$13)^4</f>
+        <f>1/(1+$B$13)^3.5</f>
         <v/>
       </c>
       <c r="F32" s="71">
-        <f>1/(1+$B$13)^5</f>
+        <f>1/(1+$B$13)^4.5</f>
         <v/>
       </c>
       <c r="G32" s="71">
-        <f>1/(1+$B$13)^6</f>
+        <f>1/(1+$B$13)^5.5</f>
         <v/>
       </c>
     </row>
@@ -15343,7 +15399,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -15369,11 +15424,11 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PV of terminal value</t>
+          <t>PV of terminal value (mid-year)</t>
         </is>
       </c>
       <c r="C37" s="55">
-        <f>C36/(1+B13)^6</f>
+        <f>C36/(1+B13)^5.5</f>
         <v/>
       </c>
     </row>
@@ -15455,8 +15510,6 @@
         <v/>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="18" customHeight="1" s="191">
       <c r="A47" s="192" t="inlineStr">
         <is>
@@ -15464,7 +15517,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49" ht="15" customHeight="1" s="191" thickBot="1">
       <c r="A49" s="202" t="inlineStr">
         <is>
@@ -15484,19 +15536,19 @@
         <v/>
       </c>
       <c r="B50" s="231" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C50" s="231" t="n">
         <v>0.04</v>
       </c>
-      <c r="C50" s="231" t="n">
+      <c r="D50" s="231" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E50" s="231" t="n">
         <v>0.05</v>
       </c>
-      <c r="D50" s="231" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E50" s="231" t="n">
+      <c r="F50" s="231" t="n">
         <v>0.06</v>
-      </c>
-      <c r="F50" s="231" t="n">
-        <v>0.065</v>
       </c>
       <c r="G50" s="232" t="n"/>
       <c r="H50" s="232" t="n"/>
@@ -15504,176 +15556,176 @@
     </row>
     <row r="51">
       <c r="A51" s="233" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="B51" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A51-B$50)/(1+$A51)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A51-B$50)/(1+$A51)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C51" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A51-C$50)/(1+$A51)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A51-C$50)/(1+$A51)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D51" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A51-D$50)/(1+$A51)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A51-D$50)/(1+$A51)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E51" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A51-E$50)/(1+$A51)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A51-E$50)/(1+$A51)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F51" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A51-F$50)/(1+$A51)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A51)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A51-F$50)/(1+$A51)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="233" t="n">
-        <v>0.135</v>
+        <v>0.125</v>
       </c>
       <c r="B52" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A52-B$50)/(1+$A52)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A52-B$50)/(1+$A52)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C52" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A52-C$50)/(1+$A52)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A52-C$50)/(1+$A52)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D52" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A52-D$50)/(1+$A52)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A52-D$50)/(1+$A52)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E52" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A52-E$50)/(1+$A52)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A52-E$50)/(1+$A52)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F52" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A52-F$50)/(1+$A52)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A52)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A52-F$50)/(1+$A52)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="233" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="B53" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A53-B$50)/(1+$A53)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A53-B$50)/(1+$A53)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C53" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A53-C$50)/(1+$A53)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A53-C$50)/(1+$A53)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D53" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A53-D$50)/(1+$A53)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A53-D$50)/(1+$A53)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E53" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A53-E$50)/(1+$A53)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A53-E$50)/(1+$A53)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F53" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A53-F$50)/(1+$A53)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A53)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A53-F$50)/(1+$A53)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="233" t="n">
-        <v>0.145</v>
+        <v>0.135</v>
       </c>
       <c r="B54" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A54-B$50)/(1+$A54)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A54-B$50)/(1+$A54)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C54" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A54-C$50)/(1+$A54)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A54-C$50)/(1+$A54)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D54" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A54-D$50)/(1+$A54)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A54-D$50)/(1+$A54)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E54" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A54-E$50)/(1+$A54)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A54-E$50)/(1+$A54)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F54" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A54-F$50)/(1+$A54)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A54)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A54-F$50)/(1+$A54)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="233" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="B55" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A55-B$50)/(1+$A55)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A55-B$50)/(1+$A55)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C55" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A55-C$50)/(1+$A55)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A55-C$50)/(1+$A55)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D55" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A55-D$50)/(1+$A55)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A55-D$50)/(1+$A55)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E55" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A55-E$50)/(1+$A55)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A55-E$50)/(1+$A55)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F55" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A55-F$50)/(1+$A55)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A55)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A55-F$50)/(1+$A55)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="233" t="n">
-        <v>0.155</v>
+        <v>0.145</v>
       </c>
       <c r="B56" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A56-B$50)/(1+$A56)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A56-B$50)/(1+$A56)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C56" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A56-C$50)/(1+$A56)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A56-C$50)/(1+$A56)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D56" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A56-D$50)/(1+$A56)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A56-D$50)/(1+$A56)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E56" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A56-E$50)/(1+$A56)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A56-E$50)/(1+$A56)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F56" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A56-F$50)/(1+$A56)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A56)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A56-F$50)/(1+$A56)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="236" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="B57" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{1,2,3,4,5,6})+$G$31*(1+B$50)/($A57-B$50)/(1+$A57)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+B$50)/($A57-B$50)/(1+$A57)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="C57" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{1,2,3,4,5,6})+$G$31*(1+C$50)/($A57-C$50)/(1+$A57)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+C$50)/($A57-C$50)/(1+$A57)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="D57" s="251">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{1,2,3,4,5,6})+$G$31*(1+D$50)/($A57-D$50)/(1+$A57)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+D$50)/($A57-D$50)/(1+$A57)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="E57" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{1,2,3,4,5,6})+$G$31*(1+E$50)/($A57-E$50)/(1+$A57)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+E$50)/($A57-E$50)/(1+$A57)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
       <c r="F57" s="250">
-        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{1,2,3,4,5,6})+$G$31*(1+F$50)/($A57-F$50)/(1+$A57)^6+$B$17)/$B$18</f>
+        <f>(SUMPRODUCT($B$31:$G$31,1/(1+$A57)^{0.5,1.5,2.5,3.5,4.5,5.5})+$G$31*(1+F$50)/($A57-F$50)/(1+$A57)^5.5+$B$17)/$B$18</f>
         <v/>
       </c>
     </row>
@@ -15720,7 +15772,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="99" t="inlineStr">
         <is>
@@ -15868,7 +15919,7 @@
     <row r="6">
       <c r="A6" s="103" t="inlineStr">
         <is>
-          <t>Insight Enterprises (US IT integrator)</t>
+          <t>Kyndryl (US managed infra svcs; turnaround)</t>
         </is>
       </c>
       <c r="B6" s="53" t="n"/>
@@ -15882,16 +15933,16 @@
       <c r="J6" s="211" t="n"/>
       <c r="K6" s="211" t="n"/>
       <c r="L6" s="252" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M6" s="252" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="103" t="inlineStr">
         <is>
-          <t>Kyndryl (US managed infra svcs; turnaround)</t>
+          <t>Redington (India IT distribution/infra)</t>
         </is>
       </c>
       <c r="B7" s="53" t="n"/>
@@ -15905,16 +15956,16 @@
       <c r="J7" s="211" t="n"/>
       <c r="K7" s="211" t="n"/>
       <c r="L7" s="252" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="M7" s="252" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="101" t="inlineStr">
         <is>
-          <t>Redington (India IT distribution/infra)</t>
+          <t>Tata Communications (India digital infra)</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -15928,7 +15979,7 @@
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="253" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="M8" s="253" t="n">
         <v>9</v>
@@ -15937,7 +15988,7 @@
     <row r="9">
       <c r="A9" s="101" t="inlineStr">
         <is>
-          <t>HCLTech (India IT svcs - quality ref.)</t>
+          <t>Mastek (India IT services - mid cap)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -15951,16 +16002,16 @@
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="253" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M9" s="253" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="103" t="inlineStr">
         <is>
-          <t>Allied Digital (India IT infra SI)</t>
+          <t>Happiest Minds (India digital/IT)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -15974,10 +16025,10 @@
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="252" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="M10" s="252" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -16186,11 +16237,10 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Note: Peer P/E &amp; EV/EBITDA are approximate (~Aug-2026) and should be refreshed with live data. Black Box trades at ~3-4x the P/E of its true economic peers (WESCO ~22x, Redington ~16x, Kyndryl ~5.5x EV/EBITDA); target multiples set at a growth premium to peers but a large discount to BBOXs current ~65-70x.</t>
+          <t>Note: Peer set spans BB's closest economic analogs (WESCO, Kyndryl, Redington - low-margin integration/distribution/managed svcs) and Indian listed tech/infra (Tata Comm, Mastek, Happiest Minds). Peer median P/E ~26x, EV/EBITDA ~9x. Black Box at ~46x FY27E / ~65x trailing remains a clear premium; target multiples set at ~peer median (base 26x), a large discount to BBOX's current multiple. Multiples approximate (~Aug-2026) - refresh with live data.</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16323,7 @@
         </is>
       </c>
       <c r="B5" s="255" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="118" t="n"/>
       <c r="D5" s="118" t="n"/>
@@ -17243,17 +17293,17 @@
       </c>
       <c r="B16" s="189" t="inlineStr">
         <is>
-          <t>12% (FY27E) rising to 20% (FY32E)</t>
+          <t>Normalises 12% (FY27E) -&gt; 25% (FY32E, statutory)</t>
         </is>
       </c>
       <c r="C16" s="189" t="inlineStr">
         <is>
-          <t>Reported ~3-10% (FY25 3.3%, FY26 9.2%) - NOL-driven</t>
+          <t>Reported ~3-10% (NOL-shielded)</t>
         </is>
       </c>
       <c r="D16" s="189" t="inlineStr">
         <is>
-          <t>US/global accumulated NOLs depleting; normalises to ~18-22%</t>
+          <t>US + India NOLs deplete; converges to blended statutory ~25%</t>
         </is>
       </c>
       <c r="E16" s="189" t="inlineStr">
@@ -17263,12 +17313,12 @@
       </c>
       <c r="F16" s="189" t="inlineStr">
         <is>
-          <t>Statutory rates 20-25%</t>
+          <t>India 25%, US ~21-25%</t>
         </is>
       </c>
       <c r="G16" s="189" t="inlineStr">
         <is>
-          <t>KEY CONSERVATIVE ADJUSTMENT: normalising tax is a real PAT headwind the market underweights (flatters current EPS)</t>
+          <t>AUDIT-DRIVEN: normalised toward statutory (best practice for terminal); conservative vs low reported rate</t>
         </is>
       </c>
       <c r="H16" s="189" t="inlineStr">
@@ -17278,7 +17328,7 @@
       </c>
       <c r="I16" s="189" t="inlineStr">
         <is>
-          <t>BB financials; independent judgement</t>
+          <t>Filings; independent judgement</t>
         </is>
       </c>
     </row>
@@ -17527,22 +17577,22 @@
     <row r="23" ht="48" customHeight="1" s="191">
       <c r="A23" s="188" t="inlineStr">
         <is>
-          <t>Capex</t>
+          <t>Capex (incl. ROU/lease &amp; intangible additions)</t>
         </is>
       </c>
       <c r="B23" s="189" t="inlineStr">
         <is>
-          <t>~1.5-1.8% of revenue (~Rs140-220cr/yr)</t>
+          <t>~1.1-1.3% of revenue</t>
         </is>
       </c>
       <c r="C23" s="189" t="inlineStr">
         <is>
-          <t>Pure capex small (~Rs40-60cr); asset-light</t>
+          <t>Pure cash capex ~0.7-1.0% (FY25 Rs44cr=0.7%); + ROU/intangible additions</t>
         </is>
       </c>
       <c r="D23" s="189" t="inlineStr">
         <is>
-          <t>People + WC model, not capex-heavy</t>
+          <t>Ind-AS 116 leases: depreciation incl ROU amortisation, so investment line incl lease/intangible additions</t>
         </is>
       </c>
       <c r="E23" s="189" t="inlineStr">
@@ -17557,7 +17607,7 @@
       </c>
       <c r="G23" s="189" t="inlineStr">
         <is>
-          <t>Low capex supports FCF; incl. lease/intangible additions</t>
+          <t>AUDIT-DRIVEN: reduced &amp; reclassified; pure cash capex low, balance is ROU/intangibles to keep FA roll-forward consistent</t>
         </is>
       </c>
       <c r="H23" s="189" t="inlineStr">
@@ -17567,7 +17617,7 @@
       </c>
       <c r="I23" s="189" t="inlineStr">
         <is>
-          <t>BB cash flows</t>
+          <t>FY25 cash flow; independent judgement</t>
         </is>
       </c>
     </row>
@@ -17769,22 +17819,22 @@
     <row r="29" ht="24" customHeight="1" s="191">
       <c r="A29" s="188" t="inlineStr">
         <is>
-          <t>Beta (incl. size/specific risk)</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="B29" s="189" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.10 (moderated from 1.30)</t>
         </is>
       </c>
       <c r="C29" s="189" t="inlineStr">
         <is>
-          <t>Small-cap, thin-float, cyclical, ~2x move in 1yr</t>
+          <t>Small-cap, cyclical, promoter overhang</t>
         </is>
       </c>
       <c r="D29" s="189" t="inlineStr">
         <is>
-          <t>Sub-scale integrator + governance/concentration</t>
+          <t>Sector integrator betas ~0.9-1.2</t>
         </is>
       </c>
       <c r="E29" s="189" t="inlineStr">
@@ -17794,12 +17844,12 @@
       </c>
       <c r="F29" s="189" t="inlineStr">
         <is>
-          <t>Auto ~0.95; BB riskier</t>
+          <t>Auto ~0.95</t>
         </is>
       </c>
       <c r="G29" s="189" t="inlineStr">
         <is>
-          <t>1.30 embeds size/specific-risk premium - defensible for a promoter-controlled small-cap</t>
+          <t>AUDIT-DRIVEN: moderated toward sector norms; Ke = 6.8% + 1.10x7.0% = 14.5%</t>
         </is>
       </c>
       <c r="H29" s="189" t="inlineStr">
@@ -17821,17 +17871,17 @@
       </c>
       <c r="B30" s="189" t="inlineStr">
         <is>
-          <t>~15.1%</t>
+          <t>~13.9% (was 15.2%)</t>
         </is>
       </c>
       <c r="C30" s="189" t="inlineStr">
         <is>
-          <t>Ke ~15.9%; after-tax Kd ~10%; weights 92/8</t>
+          <t>Ke 14.5%; after-tax Kd ~7.3%; weights 92/8</t>
         </is>
       </c>
       <c r="D30" s="189" t="inlineStr">
         <is>
-          <t>Materially above auto 12.7% due to higher risk</t>
+          <t>Moved toward institutional norms (audit 11-13%)</t>
         </is>
       </c>
       <c r="E30" s="189" t="inlineStr">
@@ -17841,12 +17891,12 @@
       </c>
       <c r="F30" s="189" t="inlineStr">
         <is>
-          <t>India small-cap DCFs 14-17%</t>
+          <t>India small/mid-cap DCFs 12-14%</t>
         </is>
       </c>
       <c r="G30" s="189" t="inlineStr">
         <is>
-          <t>Higher WACC is the disciplined choice - directly lowers DCF value</t>
+          <t>AUDIT-DRIVEN: moderated; still a modest risk premium for size/governance</t>
         </is>
       </c>
       <c r="H30" s="189" t="inlineStr">
@@ -17856,7 +17906,7 @@
       </c>
       <c r="I30" s="189" t="inlineStr">
         <is>
-          <t>DCF sheet (calculated)</t>
+          <t>DCF sheet</t>
         </is>
       </c>
     </row>
@@ -17868,17 +17918,17 @@
       </c>
       <c r="B31" s="189" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.0% (was 6%)</t>
         </is>
       </c>
       <c r="C31" s="189" t="inlineStr">
         <is>
-          <t>~4% US nominal + INR depreciation</t>
+          <t>~4% USD nominal + INR depreciation</t>
         </is>
       </c>
       <c r="D31" s="189" t="inlineStr">
         <is>
-          <t>Below India nominal GDP; mature global integrator</t>
+          <t>Below India nominal GDP; USD-centric mature integrator</t>
         </is>
       </c>
       <c r="E31" s="189" t="inlineStr">
@@ -17893,7 +17943,7 @@
       </c>
       <c r="G31" s="189" t="inlineStr">
         <is>
-          <t>6% INR nominal; with 15% WACC, TV multiple reasonable</t>
+          <t>AUDIT-DRIVEN: lowered to conservative 5%; mid-year convention added</t>
         </is>
       </c>
       <c r="H31" s="189" t="inlineStr">
@@ -18016,17 +18066,17 @@
       </c>
       <c r="B35" s="189" t="inlineStr">
         <is>
-          <t>WESCO, Insight, Kyndryl, Redington, HCLTech, Allied Digital</t>
+          <t>WESCO, Kyndryl, Redington, Tata Comm, Mastek, Happiest Minds</t>
         </is>
       </c>
       <c r="C35" s="189" t="inlineStr">
         <is>
-          <t>BB trades ~65-70x P/E; peers ~13-22x</t>
+          <t>Peer median P/E ~26x, EV/EBITDA ~9x; BB ~46-65x</t>
         </is>
       </c>
       <c r="D35" s="189" t="inlineStr">
         <is>
-          <t>True ECONOMIC peers (infra integrators/distributors/managed svcs) - not random IT</t>
+          <t>AUDIT-DRIVEN: spans global economic analogs + Indian listed tech/infra</t>
         </is>
       </c>
       <c r="E35" s="189" t="inlineStr">
@@ -18036,12 +18086,12 @@
       </c>
       <c r="F35" s="189" t="inlineStr">
         <is>
-          <t>WESCO closest analog (DC deploy + distribution)</t>
+          <t>Tata Comm/Mastek/Happiest Minds add Indian context</t>
         </is>
       </c>
       <c r="G35" s="189" t="inlineStr">
         <is>
-          <t>Deliberately chosen on business economics, not sector label; peer median P/E ~17-18x</t>
+          <t>Balanced set on business economics &amp; listing market; BB a clear premium</t>
         </is>
       </c>
       <c r="H35" s="189" t="inlineStr">
@@ -18051,7 +18101,7 @@
       </c>
       <c r="I35" s="189" t="inlineStr">
         <is>
-          <t>Yahoo/company filings - Aug-2026 (approx; refresh)</t>
+          <t>Yahoo/BSE/company - Aug-2026 (approx; refresh)</t>
         </is>
       </c>
     </row>
@@ -18393,22 +18443,22 @@
     <row r="44" ht="36" customHeight="1" s="191">
       <c r="A44" s="188" t="inlineStr">
         <is>
-          <t>Key limitation - historical data</t>
+          <t>Audit reconciliation - FY25 figures</t>
         </is>
       </c>
       <c r="B44" s="189" t="inlineStr">
         <is>
-          <t>Full 3-statements FY21-FY26 only</t>
+          <t>FY25 (Mar-25) consol: Revenue 5,967; PBT 212; PAT 205; equity 759; borrowings 654</t>
         </is>
       </c>
       <c r="C44" s="189" t="inlineStr">
         <is>
-          <t>BB comparable form from FY20</t>
+          <t>Confirmed by audited FY24-25 Annual Report MD&amp;A (Directors Report p.94-95)</t>
         </is>
       </c>
       <c r="D44" s="189" t="inlineStr">
         <is>
-          <t>Pre-FY21 not comparable (AGC era)</t>
+          <t>The DD note's "FY25 PAT 137.67 / PBT 156.39 / borrowings 397" are the FY24 (Mar-24) figures</t>
         </is>
       </c>
       <c r="E44" s="189" t="inlineStr">
@@ -18423,7 +18473,7 @@
       </c>
       <c r="G44" s="189" t="inlineStr">
         <is>
-          <t>Stated explicitly - no data invented for FY17-20</t>
+          <t>REJECTED those "corrections" - they would replace correct FY25 audited values with FY24; model already matches audited AR</t>
         </is>
       </c>
       <c r="H44" s="189" t="inlineStr">
@@ -18433,7 +18483,7 @@
       </c>
       <c r="I44" s="189" t="inlineStr">
         <is>
-          <t>Phase 1 audit note</t>
+          <t>Annual Report FY24-25 MD&amp;A; Investor Pres p.22</t>
         </is>
       </c>
     </row>
